--- a/output/full_scan/batch_seq1_2026-08-28.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-28.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1040.629404870624</v>
+        <v>1040.629404870625</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>66</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.98512601520668</v>
+        <v>59.98512603201439</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17.57465382401211</v>
+        <v>17.57465384118926</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.194834990775525</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.6475740029573369</v>
+        <v>0.6475740028015573</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -580,21 +580,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1531</v>
+        <v>1569</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>724</v>
+        <v>876.1474611979993</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13.7</v>
+        <v>46.3</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>78.23895575423585</v>
+        <v>60.43261761464826</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15.82056379664666</v>
+        <v>20.07347618820116</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6.212098493557268</v>
+        <v>2.391598223764575</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0578118766220559</v>
+        <v>0.4872607851879863</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1558</v>
+        <v>1303</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>614.1653659852367</v>
+        <v>870.7455893356438</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>102</v>
+        <v>220.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.96766375377308</v>
+        <v>62.69150944731723</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>28.49430766906542</v>
+        <v>15.61506719871635</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4802497691106879</v>
+        <v>1.889091264621793</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.3808061334059558</v>
+        <v>2.696649588631918</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1514</v>
+        <v>1531</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>609.2127172723713</v>
+        <v>864</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>105</v>
+        <v>13.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>53.02168029359571</v>
+        <v>78.23895501917895</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21.73074537579748</v>
+        <v>15.82056412126508</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4.119494345730442</v>
+        <v>6.212098493557268</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.03975230907926</v>
+        <v>0.0578118768414689</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1402</v>
+        <v>1301</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>593.9251572270491</v>
+        <v>824.8617849073908</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.1</v>
+        <v>62.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>50.6910108766392</v>
+        <v>60.71935578736472</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.92809871020169</v>
+        <v>16.15608607543937</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4883271372226249</v>
+        <v>1.272158954139876</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.055435934319683</v>
+        <v>0.5470290002965412</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1440</v>
+        <v>1229</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>592.8295327171352</v>
+        <v>781.7810705171756</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13.7</v>
+        <v>42.15</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>57.08378413687997</v>
+        <v>57.13539723680782</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.01852389056485</v>
+        <v>17.17495122822585</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6099991668769855</v>
+        <v>0.5596191024292493</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.0461915896635517</v>
+        <v>0.1176272007346319</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1455</v>
+        <v>1312</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>587.9540980251666</v>
+        <v>751</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>14.15</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.19512370561158</v>
+        <v>69.6022711990129</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26.03671607884537</v>
+        <v>17.04528648986314</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6850608383404502</v>
+        <v>14.19495946964225</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0229958519182701</v>
+        <v>0.3178118521494725</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1416</v>
+        <v>1582</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>553.6304415671618</v>
+        <v>743.0578484325825</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11.8</v>
+        <v>76.8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.94447938893094</v>
+        <v>58.05620259640506</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>31.28305451536681</v>
+        <v>18.59822897247575</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2786446382406921</v>
+        <v>1.726370483258951</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0214059817406176</v>
+        <v>0.78110269373631</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1439</v>
+        <v>1324</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>532.9536657660054</v>
+        <v>731.5893179075746</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>29.4</v>
+        <v>10.25</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.19574534383871</v>
+        <v>57.28819182069232</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10.08829225588892</v>
+        <v>14.66327478655324</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6212922390738111</v>
+        <v>1.742751273355172</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.0888028437426652</v>
+        <v>0.0318343499808109</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1524</v>
+        <v>1213</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>528.9306401547627</v>
+        <v>721.7812392729035</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>27.5</v>
+        <v>7.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>55.06871273112017</v>
+        <v>52.67025127900784</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15.91378202827765</v>
+        <v>11.38047453194312</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6264022139929429</v>
+        <v>3.859087433434207</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1185045820561655</v>
+        <v>0.0418844496870708</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1504</v>
+        <v>1455</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>515.185079804989</v>
+        <v>697.9540980251666</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>59.1351864452001</v>
+        <v>59.19512357765436</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.18489306703719</v>
+        <v>26.03671609698415</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.357098740618036</v>
+        <v>0.6850608383404502</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.3541855225224644</v>
+        <v>0.0229958519564292</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1503</v>
+        <v>1323</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>494.0393953487191</v>
+        <v>687.1663896517322</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>205.5</v>
+        <v>21.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>52.49822364652406</v>
+        <v>62.0937020111213</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.43180736538329</v>
+        <v>23.63396154256749</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.252555054291607</v>
+        <v>0.3561212233743175</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.853344395538448</v>
+        <v>-0.0151694929722056</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1560</v>
+        <v>1319</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>483.5686642080937</v>
+        <v>681.4909202599397</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>695</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>51.26917634147837</v>
+        <v>60.23592584582829</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>8.081717118677778</v>
+        <v>33.50133379711308</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4785125155741455</v>
+        <v>0.9933662980973432</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.180588751287216</v>
+        <v>0.2551162464209673</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1419</v>
+        <v>1560</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>483.3761302664757</v>
+        <v>668.5686642080935</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>695</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.10344459344202</v>
+        <v>51.26917641082274</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15.50199104847775</v>
+        <v>8.081717131063071</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.8505047006936451</v>
+        <v>0.4785125155741455</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.25621673140914</v>
+        <v>-1.180588751001006</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1515</v>
+        <v>1416</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>477.9919796596084</v>
+        <v>663.6304415671618</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34.7</v>
+        <v>11.8</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>54.09439219066064</v>
+        <v>61.94447918187806</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.32663264449882</v>
+        <v>31.28305449030781</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.238302499247717</v>
+        <v>0.2786446382406921</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4374934426396027</v>
+        <v>0.0214059817692367</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>475.7807805066881</v>
+        <v>650.7642933903226</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>22.9</v>
+        <v>17.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.20415161017927</v>
+        <v>48.00421316461896</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20.6787363807768</v>
+        <v>38.61086137144609</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9394411035896468</v>
+        <v>2.36992441191095</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1112833179911888</v>
+        <v>0.2177793063364917</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1414</v>
+        <v>1528</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>474.7642781832174</v>
+        <v>646.7550833705228</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>19.3</v>
+        <v>19.55</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>50.02175875133207</v>
+        <v>52.48394298507613</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.10910598779743</v>
+        <v>25.34743521293213</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.421197260026078</v>
+        <v>1.094877022213976</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.1223842328800385</v>
+        <v>0.2462112556863575</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1442</v>
+        <v>1524</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>471.7948136220599</v>
+        <v>638.9306401547626</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>29.85</v>
+        <v>27.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.25520167483691</v>
+        <v>55.06871276146573</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.17993846478808</v>
+        <v>15.91378201916532</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6591210032457149</v>
+        <v>0.6264022139929429</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.046442940585985</v>
+        <v>0.1185045819798499</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1519</v>
+        <v>1316</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>439.3325514112145</v>
+        <v>636.7714907141033</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>755</v>
+        <v>11.15</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.14575326797581</v>
+        <v>57.6970810378801</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.19629750045708</v>
+        <v>28.7816026955104</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.289892004895932</v>
+        <v>2.277149071410326</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>7.702495575112458</v>
+        <v>0.1280794338702602</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1409</v>
+        <v>1504</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>428.8442192002486</v>
+        <v>630.1850798049891</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>24.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>50.42972881469711</v>
+        <v>59.13518642068755</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9.004535440762385</v>
+        <v>22.1848930647012</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.681895200012229</v>
+        <v>1.357098740618036</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1130545935294947</v>
+        <v>0.3541855224270809</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1341</v>
+        <v>1326</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>425.5224047664328</v>
+        <v>627.9585906406141</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>60.1</v>
+        <v>62.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>53.48207147604987</v>
+        <v>54.7955304979807</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14.78524634984595</v>
+        <v>12.32566112254297</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.1194878749678876</v>
+        <v>0.9975866606838186</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.81011454699025</v>
+        <v>0.4203555826988802</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1459</v>
+        <v>1341</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>411.6044130733094</v>
+        <v>625.5224047664328</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>15.55</v>
+        <v>60.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>78.79521112373573</v>
+        <v>53.48207147474539</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>44.93595590072073</v>
+        <v>14.78524634741845</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5604413073309421</v>
+        <v>0.1194878749678876</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1250516937487972</v>
+        <v>0.81011454699025</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1513</v>
+        <v>1256</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>404.3765685990337</v>
+        <v>624.3625267096226</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.77724175846931</v>
+        <v>58.92589824669453</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>14.85428328750759</v>
+        <v>10.95308210842165</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8272576558085414</v>
+        <v>1.292459260824782</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.6044529198379636</v>
+        <v>1.096694564861427</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>400.3510057623499</v>
+        <v>614.1653659852367</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11.25</v>
+        <v>102</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46.68886167022975</v>
+        <v>64.96766372632018</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>38.3822929823843</v>
+        <v>28.49430770758451</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5555129634207643</v>
+        <v>0.4802497691106879</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0576582347407477</v>
+        <v>0.3808061332151649</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1470</v>
+        <v>1514</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>399.5868343145309</v>
+        <v>609.212717272371</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>23.55</v>
+        <v>105</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>52.02055309393229</v>
+        <v>53.02168027805664</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>9.750552233532025</v>
+        <v>21.73074541473109</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3627459871225174</v>
+        <v>4.119494345730442</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0547594463502847</v>
+        <v>1.039752308697682</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1528</v>
+        <v>1503</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>396.7550833705232</v>
+        <v>609.0393953487192</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>19.55</v>
+        <v>205.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.48394298507613</v>
+        <v>52.49822367850334</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.34743515064929</v>
+        <v>18.43180741122721</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.094877022213976</v>
+        <v>2.252555054291607</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.2462112557149773</v>
+        <v>1.853344394870684</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1521</v>
+        <v>1402</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>392.7404577244769</v>
+        <v>593.9251572270491</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>25.9</v>
+        <v>28.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.31192597678513</v>
+        <v>50.69101083498872</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>14.65866262820962</v>
+        <v>20.92809874442131</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.313661128219011</v>
+        <v>0.4883271372226249</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.07046467036099451</v>
+        <v>0.0554359342338287</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1434</v>
+        <v>1515</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>361.9987486650216</v>
+        <v>592.9919796596084</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>17.85</v>
+        <v>34.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.56427816405633</v>
+        <v>54.0943921809841</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>27.07839009297972</v>
+        <v>22.32663268871168</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.231767024135537</v>
+        <v>2.238302499247717</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0421638737778887</v>
+        <v>0.4374934426396027</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1530</v>
+        <v>1440</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>360.4295113904797</v>
+        <v>592.8295327171352</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>29</v>
+        <v>13.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.37062960805857</v>
+        <v>57.08378402591779</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>13.45592612018676</v>
+        <v>23.01852388412265</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.652826805109171</v>
+        <v>0.6099991668769855</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.08488344541028731</v>
+        <v>0.0461915896826322</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1451</v>
+        <v>1414</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>352.7690977351194</v>
+        <v>584.7642781832174</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.04756917150919</v>
+        <v>50.02175862383111</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>18.1329830752797</v>
+        <v>21.10910602666753</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8372371616605218</v>
+        <v>1.421197260026078</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0212660767013771</v>
+        <v>-0.1223842328800385</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1568</v>
+        <v>1315</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>349.2042056020273</v>
+        <v>573.4417810256243</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>29.1</v>
+        <v>65.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>47.16392450504276</v>
+        <v>55.63973180078384</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>12.2614888145884</v>
+        <v>32.58347832385285</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6161961740300491</v>
+        <v>1.22825849952198</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.271773247776481</v>
+        <v>-0.0036399979150332</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1437</v>
+        <v>1110</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>342.1660455490841</v>
+        <v>562.3059589987867</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>31.95</v>
+        <v>15.95</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.57850288164018</v>
+        <v>49.28578481344542</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.14096648170313</v>
+        <v>26.52200316996083</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.0475975897609682</v>
+        <v>0.1079250379525157</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.056934433228724</v>
+        <v>-0.0319727827337745</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1435</v>
+        <v>1519</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>337.4486789992685</v>
+        <v>554.3325514112148</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>22</v>
+        <v>755</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.20072240701142</v>
+        <v>59.14575333180253</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6.69779598690008</v>
+        <v>15.19629754313165</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6396693694292703</v>
+        <v>2.289892004895932</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.2579478143009547</v>
+        <v>7.702495573013721</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>329.3070199092426</v>
+        <v>551.6044130733094</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11.25</v>
+        <v>15.55</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>49.50780091513215</v>
+        <v>78.79521103167068</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.61336494238147</v>
+        <v>44.93595623097872</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8097309647897579</v>
+        <v>0.5604413073309421</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0309427595556265</v>
+        <v>0.1250516937651459</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1533</v>
+        <v>1321</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>328.7107322756297</v>
+        <v>550.3806943453968</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>32.2</v>
+        <v>33.15</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46.78465713633263</v>
+        <v>60.78550105542189</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>27.35055940365857</v>
+        <v>17.92863630197932</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.734989177575973</v>
+        <v>1.074807061795136</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1640591558134995</v>
+        <v>0.1409575982483181</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>327.9189768560353</v>
+        <v>532.9536657660054</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>38.55</v>
+        <v>29.4</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.32902047877206</v>
+        <v>61.19574540627678</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.00328191570312</v>
+        <v>10.08829233740032</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3520347908194196</v>
+        <v>0.6212922390738111</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4540643604740144</v>
+        <v>-0.0888028437999008</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1472</v>
+        <v>1102</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>321.1961175254607</v>
+        <v>486.3333283728874</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>34.55</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>18.25864277997102</v>
+        <v>56.47887338580453</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>8.96132077644242</v>
+        <v>23.88918498271878</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.0051660505835156</v>
+        <v>0.8298718137019001</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-5.500605590675976</v>
+        <v>0.239200239279095</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1541</v>
+        <v>1308</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>315.160665397899</v>
+        <v>485.7672779878922</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>21.7</v>
+        <v>13.85</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.49474320384618</v>
+        <v>52.7214020503914</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.60304032998972</v>
+        <v>21.32085912295194</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4494167413353857</v>
+        <v>0.9729757747237084</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0034032590737292</v>
+        <v>0.0922382319899305</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1340</v>
+        <v>1419</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>312.4897271034466</v>
+        <v>483.3761302664755</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>5.23</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.84506468712191</v>
+        <v>55.10344468467847</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16.71434789216156</v>
+        <v>15.50199112810779</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5960431973090201</v>
+        <v>0.8505047006936451</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.027051165752487</v>
+        <v>0.2562167312374151</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1525</v>
+        <v>1236</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>311.5097830803135</v>
+        <v>482.9263892956372</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>66.5</v>
+        <v>25.55</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>44.36174012005915</v>
+        <v>59.16202102233353</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.69200702316108</v>
+        <v>22.63753607218936</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7066356844965525</v>
+        <v>1.04723342297041</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.1642092836342163</v>
+        <v>0.0233005872140159</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1516</v>
+        <v>1101</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>306.2451434436734</v>
+        <v>481.433765877759</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>14.75</v>
+        <v>24.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.57567475434401</v>
+        <v>50.64572649274533</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29.26324911265113</v>
+        <v>24.03632655194286</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4947055939980602</v>
+        <v>0.6290034541275229</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.3461480910850874</v>
+        <v>-0.0278522375328013</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1342</v>
+        <v>1532</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>302.1400498230546</v>
+        <v>475.7807805066882</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>104</v>
+        <v>22.9</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.0057985900399</v>
+        <v>57.20415176599476</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>18.03924072937893</v>
+        <v>20.67873637652018</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.522638649092517</v>
+        <v>0.9394411035896468</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.4788742486715449</v>
+        <v>0.1112833178957927</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1417</v>
+        <v>1442</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>284.5107893594377</v>
+        <v>471.7948136220599</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>29.85</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46.30039749159064</v>
+        <v>51.25520174582094</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.42269199401889</v>
+        <v>23.17993853706572</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6602377542150697</v>
+        <v>0.6591210032457149</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.015263314687942</v>
+        <v>-0.046442940643223</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>266.8711173293147</v>
+        <v>470.4295113904797</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>32.7</v>
+        <v>29</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>44.62493958280385</v>
+        <v>50.37062959115189</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.01235447864195</v>
+        <v>13.4559261517658</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8255394977949376</v>
+        <v>0.652826805109171</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0158968105390381</v>
+        <v>0.0848834453625891</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1452</v>
+        <v>1471</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>261.8217190830163</v>
+        <v>448.1408324258752</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.88408749311928</v>
+        <v>54.46922811577871</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14.05356212882439</v>
+        <v>31.24132491568896</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.113580291501229</v>
+        <v>0.7770735968331418</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0040510666143793</v>
+        <v>0.098066806823109</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1536</v>
+        <v>1435</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>260.8815048367712</v>
+        <v>447.4486789992685</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>50.3</v>
+        <v>22</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.00020988254565</v>
+        <v>46.20070634521782</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13.325839361582</v>
+        <v>6.697795920548842</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7679703440038008</v>
+        <v>0.6396693694292703</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0106172934368083</v>
+        <v>-0.2579478171219188</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1477</v>
+        <v>1232</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>258.1199197939949</v>
+        <v>445.5540689189104</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>195.5</v>
+        <v>156.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>33.65313685588536</v>
+        <v>54.40961263480961</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.08404341274446</v>
+        <v>27.25645605436491</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5229036261538267</v>
+        <v>0.5571849376402841</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.346373024733937</v>
+        <v>0.0026404109700024</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1473</v>
+        <v>1225</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>252.0777221370638</v>
+        <v>440.5402734589306</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>20</v>
+        <v>25.45</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.27370981078953</v>
+        <v>49.82560680364482</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7.480627008050448</v>
+        <v>28.01867166603608</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5843331229888256</v>
+        <v>2.157478502972904</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0285317270023074</v>
+        <v>0.2797570408395794</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1526</v>
+        <v>1434</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>249.2235043401943</v>
+        <v>436.9987486650216</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>16.45</v>
+        <v>17.85</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45.55601707378336</v>
+        <v>51.56427811922103</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.46961862010145</v>
+        <v>27.07839007157072</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.1832680812705203</v>
+        <v>1.231767024135537</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.2272437445695268</v>
+        <v>0.04216387379697</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1438</v>
+        <v>1233</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>246.3551306248868</v>
+        <v>432.160870589137</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>22.35</v>
+        <v>28.9</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.12680843426422</v>
+        <v>61.20279585177476</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8.943483362011502</v>
+        <v>23.08363765120216</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7079031626962317</v>
+        <v>0.3045969326352387</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0244897431108022</v>
+        <v>0.08569781435000209</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1441</v>
+        <v>1409</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>235.0759821844686</v>
+        <v>428.8442192002486</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9.09</v>
+        <v>24.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.64022420366752</v>
+        <v>50.42972878075694</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18.18015527689193</v>
+        <v>9.004535440762385</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.046249962988186</v>
+        <v>1.681895200012229</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0351620055415472</v>
+        <v>0.1130545935676555</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1540</v>
+        <v>1525</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>231.2693389450297</v>
+        <v>421.5097830803135</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>19.35</v>
+        <v>66.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>40.43274580672653</v>
+        <v>44.36174026670214</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>22.37811650138385</v>
+        <v>22.69200715984822</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6207355863814717</v>
+        <v>0.7066356844965525</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.09186377170286809</v>
+        <v>-0.164209283958565</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1537</v>
+        <v>1217</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>230.7506680342573</v>
+        <v>418.0668512985077</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>119</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>25.85377845091573</v>
+        <v>52.35268481592177</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>27.23302129089885</v>
+        <v>14.23076499319825</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9412993325322838</v>
+        <v>0.7762354858348766</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.7063825515010194</v>
+        <v>0.0073152634220605</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1465</v>
+        <v>1513</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>227.9236023862693</v>
+        <v>414.3765685990337</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>40.17984158555432</v>
+        <v>54.77724179913078</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>22.00286653343868</v>
+        <v>14.85428329769956</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.840766137969606</v>
+        <v>0.8272576558085414</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0101064615885791</v>
+        <v>0.6044529195517878</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1506</v>
+        <v>1517</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>223.5027074479312</v>
+        <v>400.3510057623499</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>10.15</v>
+        <v>11.25</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.21367757326017</v>
+        <v>46.68886178278572</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.43638098813868</v>
+        <v>38.38229322705735</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.910637834293344</v>
+        <v>0.5555129634207643</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.01098940742364</v>
+        <v>-0.0576582348075257</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1418</v>
+        <v>1470</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>221.987340276978</v>
+        <v>399.5868343145309</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>17.75</v>
+        <v>23.55</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>42.48838949533501</v>
+        <v>52.02055314999829</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.58818556552824</v>
+        <v>9.750552188598819</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5086854351932912</v>
+        <v>0.3627459871225174</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.008363919876929001</v>
+        <v>-0.0547594463979818</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1413</v>
+        <v>1521</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>211.6831832500557</v>
+        <v>392.740457724477</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>9.31</v>
+        <v>25.9</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.68624629499795</v>
+        <v>56.31192603219935</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8.402653237834187</v>
+        <v>14.65866275260022</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3585426628055761</v>
+        <v>1.313661128219011</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0019524597075567</v>
+        <v>0.0704646702846787</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1468</v>
+        <v>1325</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>206.4737590266643</v>
+        <v>380.628896120975</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>13.3</v>
+        <v>26.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.41951210015272</v>
+        <v>51.1023174918727</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.28957291662007</v>
+        <v>27.52271072592247</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.976598703590152</v>
+        <v>0.4904176688261172</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0428579881893885</v>
+        <v>-0.0360032362247914</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1447</v>
+        <v>1339</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>205.7537974810296</v>
+        <v>377.7537864776314</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>6.88</v>
+        <v>43.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.5001196411397</v>
+        <v>39.34588577532944</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.92316488572118</v>
+        <v>17.90661911787113</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6863533828044014</v>
+        <v>0.8422409202980388</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0120664411519726</v>
+        <v>-0.2483853323287562</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1445</v>
+        <v>1201</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>202.148449332716</v>
+        <v>371.6308643096501</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>48.36667254487582</v>
+        <v>47.97641600488284</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13.54691249660878</v>
+        <v>8.545306421731706</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.356690742023294</v>
+        <v>0.9550590366914592</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0516750699475068</v>
+        <v>0.0065095985054052</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1522</v>
+        <v>1210</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>201.0664332427977</v>
+        <v>371.3194686602441</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.61042139336138</v>
+        <v>35.30713061696429</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.33825947868913</v>
+        <v>31.00734310668929</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.701159147044728</v>
+        <v>0.6880976847637199</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0841151787663037</v>
+        <v>0.0059669971107458</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1476</v>
+        <v>1451</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>199.6928570360291</v>
+        <v>352.7690977351194</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>311.5</v>
+        <v>17.4</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>38.03556590999911</v>
+        <v>52.04756920427295</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.54073276908075</v>
+        <v>18.1329830752797</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5006298377903391</v>
+        <v>0.8372371616605218</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.303646521350659</v>
+        <v>-0.0212660766823</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1454</v>
+        <v>1215</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>199.4209322513092</v>
+        <v>352.4395630537803</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>12.45</v>
+        <v>108.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.69346296116696</v>
+        <v>47.38124315994252</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>28.68419703966916</v>
+        <v>22.07373015583212</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3121439061735082</v>
+        <v>0.6165276071492296</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0061482154994481</v>
+        <v>0.2761371374373353</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1466</v>
+        <v>1568</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>196.4918882489825</v>
+        <v>349.2042056020273</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>15.9</v>
+        <v>29.1</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.19632383076478</v>
+        <v>47.16392456532432</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.27077858389327</v>
+        <v>12.26148888521808</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9273361160865377</v>
+        <v>0.6161961740300491</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0566679288811783</v>
+        <v>0.2717732477097047</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1463</v>
+        <v>1314</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>192.8436006473201</v>
+        <v>345.8406284420403</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>17.4</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>39.93973802825354</v>
+        <v>52.05764011402981</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.56291737030068</v>
+        <v>17.61210886812692</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3018215844437917</v>
+        <v>0.7669062443649611</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0318364796955989</v>
+        <v>0.0561732952999324</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1446</v>
+        <v>1310</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>187.8173101358458</v>
+        <v>345.2710629881205</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>13.65</v>
+        <v>8.43</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>36.40577132278202</v>
+        <v>50.06402826776655</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>36.15144101998853</v>
+        <v>15.00899486448505</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.545343327558432</v>
+        <v>1.226717974061621</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0548951244956941</v>
+        <v>0.1153658963083976</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1457</v>
+        <v>1437</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>184.4758753929044</v>
+        <v>342.1660455490841</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>14.45</v>
+        <v>31.95</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.82297287725064</v>
+        <v>58.57850286687393</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.48627739025632</v>
+        <v>21.14096648170313</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4790271290288763</v>
+        <v>0.0475975897609682</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0127565388062264</v>
+        <v>0.0569344332478027</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1410</v>
+        <v>1465</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>180.8025361843346</v>
+        <v>337.9236023862693</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>24.4</v>
+        <v>12</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>35.60132860339303</v>
+        <v>40.17984156759582</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>12.08909978766087</v>
+        <v>22.00286653677149</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.159944848016634</v>
+        <v>1.840766137969606</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1314118697528911</v>
+        <v>-0.0101064615981184</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1423</v>
+        <v>1313</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>177.6147067430591</v>
+        <v>337.6317045341411</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>34.95</v>
+        <v>11.85</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>39.29005574482873</v>
+        <v>52.76661499827178</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14.28783646418448</v>
+        <v>14.37018372648029</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.463215267983665</v>
+        <v>1.15459034150262</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0724431546221339</v>
+        <v>0.0757432127039334</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1444</v>
+        <v>1220</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>176.2550833006978</v>
+        <v>336.4204768632318</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>7.17</v>
+        <v>10.9</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.19280654122107</v>
+        <v>33.86390037132414</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.10883120921738</v>
+        <v>29.76906316675451</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6588667355599884</v>
+        <v>1.226421167499274</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0156987407041358</v>
+        <v>0.005817073057531</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1467</v>
+        <v>1536</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>169.1220136690297</v>
+        <v>335.8815048367712</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>8.279999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>41.15797167909901</v>
+        <v>50.00020988254565</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.91019918895658</v>
+        <v>13.32583946690637</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4064657559740383</v>
+        <v>0.7679703440038008</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.08665837126167431</v>
+        <v>-0.0106172936085228</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1432</v>
+        <v>1453</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>167.3046739545048</v>
+        <v>329.3070199092426</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>15.05</v>
+        <v>11.25</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.32283437895747</v>
+        <v>49.50780089507218</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.0401066608274</v>
+        <v>26.61336491261103</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7200471772789159</v>
+        <v>0.8097309647897579</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0177786814534286</v>
+        <v>0.0309427595651667</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>166.4524398937122</v>
+        <v>328.7107322756297</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0</v>
+        <v>32.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.94801338254422</v>
+        <v>46.78465710988818</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10.52820967082107</v>
+        <v>27.35055945301355</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.001431229426077</v>
+        <v>0.734989177575973</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.1543698819305701</v>
+        <v>0.1640591558230379</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1456</v>
+        <v>1436</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>152.2078990889501</v>
+        <v>327.9189768560353</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>13.65</v>
+        <v>38.55</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.77683623715181</v>
+        <v>48.32902052114984</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19.75174028912599</v>
+        <v>21.00328186107763</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9205283132805068</v>
+        <v>0.3520347908194196</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0059488650348843</v>
+        <v>0.4540643602832178</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1464</v>
+        <v>1305</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>149.4425738835937</v>
+        <v>327.3378458634488</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>10.15</v>
+        <v>12.1</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.27321895646322</v>
+        <v>51.78641292061892</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9.895786883853329</v>
+        <v>13.30702024375912</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8834447206290561</v>
+        <v>1.305909569107919</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0112189345679603</v>
+        <v>0.1033518061096071</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1460</v>
+        <v>1203</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>138.4743461533372</v>
+        <v>326.7622666013528</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>6.62</v>
+        <v>45.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.67076642766637</v>
+        <v>48.26298135393273</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.9657149859854</v>
+        <v>16.89801508990736</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6715920108997665</v>
+        <v>0.6448224522573006</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0221472090385823</v>
+        <v>-0.0202269079232612</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1475</v>
+        <v>1342</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>130.6217509783445</v>
+        <v>322.1400498230546</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>26.6</v>
+        <v>104</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.04633202040282</v>
+        <v>49.00579856471612</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.33040870746116</v>
+        <v>18.03924091346754</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6470483565707025</v>
+        <v>0.522638649092517</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.07194174629693099</v>
+        <v>0.478874248518919</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1539</v>
+        <v>1472</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>123.9115792744166</v>
+        <v>321.1961175254607</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>15.65</v>
+        <v>0</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>41.01996150611962</v>
+        <v>18.25864276779894</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>12.42177442493232</v>
+        <v>8.961320844304909</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4311370101520761</v>
+        <v>0.0051660505835156</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0483669154130413</v>
+        <v>-5.500605590389779</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1474</v>
+        <v>1541</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>109.1372536294905</v>
+        <v>315.1606653978989</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>10</v>
+        <v>21.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>43.34104251574254</v>
+        <v>49.49474319386184</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.98760222617126</v>
+        <v>21.60304033359736</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.342117553950949</v>
+        <v>0.4494167413353857</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0060955373201013</v>
+        <v>0.0034032590355721</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1512</v>
+        <v>1219</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>97.80651653183772</v>
+        <v>314.4904762914676</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>6.41</v>
+        <v>11.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>36.22119210977937</v>
+        <v>52.60357190914017</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>9.548114516495328</v>
+        <v>21.0654955619511</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5238506627744138</v>
+        <v>0.9916185961456632</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0098910222206758</v>
+        <v>0.1204818678901875</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1443</v>
+        <v>1340</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>96.79947483767459</v>
+        <v>312.4897271034466</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>24.9</v>
+        <v>5.23</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>50.35447493833495</v>
+        <v>50.84506467821759</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7.577316542358669</v>
+        <v>16.71434790215493</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.444324430479183</v>
+        <v>0.5960431973090201</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,62 +4810,2712 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.2616461730510334</v>
+        <v>0.027051165739132</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
+        <v>1466</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>聚隆</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>306.4918882489825</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>45.19632381308998</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>12.27077867763909</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.9273361160865377</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-0.0566679288430213</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>川飛</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>306.2451434436734</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>49.57567473787224</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>29.26324913148699</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.4947055939980602</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>0.3461480911137066</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>嘉裕</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>284.5107893594377</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>46.30039756898424</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>14.4226920220486</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.6602377542150697</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0.0152633146784034</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>聯華食</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>281.3077680951178</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>39.84486099895262</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>14.97011767767186</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.7416158456348211</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>0.1734846618030487</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>279.0876390050997</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>45.66009040315755</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>14.66519665134927</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.7661207308929707</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.0561853262149572</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>台聚</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>275.7327401356891</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>48.17967541228703</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>13.33008750871188</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>1.196577582800366</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.0935444012000546</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>台達化</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>274.030542210826</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>46.63900109638384</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>13.72077815925815</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>1.205292150271437</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.1270845895688141</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>鑽全</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>266.8711173293148</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>44.62493953123994</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>12.01235463086541</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.8255394977949376</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0.0158968105104194</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>信大</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>266.3532571510092</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>40.19640831778865</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>25.4682966619722</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.5827047439375282</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>0.0314171050861418</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>南緯</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>264.1220136690297</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>41.1579716830189</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>13.91019920323392</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.4064657559740383</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-0.086658371265491</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>1452</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>宏益</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>261.8217190830163</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>48.88408769984991</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>14.05356215595189</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>1.113580291501229</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-0.0040510666239178</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>1477</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>聚陽</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>258.1199197939949</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>33.65313682521784</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>23.0840434432932</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.5229036261538267</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-1.346373024733937</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>252.0777221370638</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>49.27370935754188</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>7.480626978068979</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.5843331229888256</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0.0285317270404671</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>1526</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>日馳</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>249.2235043401943</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>45.55601705034566</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>26.46961869217231</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.1832680812705203</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>-0.2272437445695268</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>1438</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>三地開發</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>246.3551306248868</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>50.1268089461329</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>8.943483224399177</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.7079031626962317</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-0.0244897434542308</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>1475</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>業旺</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>240.6217509783447</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>51.04633201173323</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>15.33040869200769</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.6470483565707025</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.0719417461824547</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>三芳</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>236.3137750006041</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>43.47051334165342</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>22.41586302331267</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.955671997877604</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>0.0887375861828531</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>大東</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>235.0759821844687</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>53.64022428099271</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>18.18015530890607</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1.046249962988186</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0.0351620055320068</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>喬福</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>231.2693389450297</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>40.4327458487395</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>22.3781165074851</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.6207355863814717</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>0.0918637716456332</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>廣隆</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>230.7506680342576</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>25.85377848525522</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>27.2330212826824</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.9412993325322838</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.7063825516918201</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>正道</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>223.5027074479312</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>44.21367759450784</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>12.43638097491381</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.910637834293344</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-0.0109894074427206</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>東華</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>221.987340276978</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>42.48838939251804</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>16.58818558122798</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.5086854351932912</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>0.0083639198960066</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>1474</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>弘裕</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>219.1372536294905</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>43.3410424718312</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>14.98760224616214</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.342117553950949</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0.0060955373391818</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>1413</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>宏洲</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>211.6831832500557</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>46.68624645018526</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>8.402653143915302</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.3585426628055761</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>-0.0019524597361759</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>廣華-KY</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>206.802843113997</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>28.75920135397168</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>43.93325936658601</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>1.02812822722834</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-0.0072984891972178</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>1468</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>206.4737590266643</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>51.41951211659303</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>16.28957306211024</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.976598703590152</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-0.0428579882370862</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>力鵬</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>205.7537974810296</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>45.50011964710488</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>11.92316484810441</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.6863533828044014</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0.0120664411443412</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>嘉泥</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>203.0636318941812</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>45.84458022007628</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>12.54949448510696</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.7216122638032191</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.0188754012411347</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>大宇</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>202.148449332716</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>48.3666725081147</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>13.54691253868906</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.356690742023294</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.0516750699284264</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>堤維西</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>201.0664332427977</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>45.61042126022325</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>12.33825942417515</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.701159147044728</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>0.0841151787281451</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>1476</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>儒鴻</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>199.6928570360287</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>311.5</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>38.03556594231922</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>19.54073270266571</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.5006298377903391</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-1.303646525643552</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>台富</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>199.4209322513092</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>44.69346306968068</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>28.68419704475437</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.3121439061735082</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.0061482155280663</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>幸福</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>195.3619573457291</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>35.50154158272981</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>52.35173723254849</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.4147881171695615</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.050806474597777</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>1463</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>強盛新</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>192.8436006473201</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>39.93973798829724</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>14.56291736990448</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.3018215844437917</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.0318364797146788</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>1446</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>宏和</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>187.8173101358458</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>36.40577151769072</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>36.15144101812762</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.545343327558432</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.0548951243812164</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>1432</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>大魯閣</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>187.3046739545048</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>43.32283437895747</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>14.04010668876606</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.7200471772789159</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0.0177786814534286</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>宜進</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>184.4758753929044</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>53.82297302520372</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>14.48627724968456</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.4790271290288763</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>0.0127565387871461</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>南染</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>180.8025361843346</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>35.60132878364124</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>12.08909989146244</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>1.159944848016634</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>-0.131411869991383</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>177.6147067430591</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>39.29006773633333</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>14.28784246263484</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>1.463215267983665</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>0.07244314743872569</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>1444</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>力麗</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>176.2550833006978</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>44.19280654825391</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>17.10883125297696</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.6588667355599884</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>0.0156987406907807</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>環泥</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>170.1413757012076</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>43.46404171371184</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>10.10849211837788</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>1.320716647093213</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0.0251599206193949</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>1538</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>正峰</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>166.4524398937122</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>45.94801420178681</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>10.52820993751385</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.001431229426077</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>-0.1543698868339882</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>156.6398647545354</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>42.91300746383975</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>11.84030314736939</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.9519674431863224</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.0065784594361227</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>1456</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>152.2078990889501</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>46.77683612429031</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>19.75174037654614</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.9205283132805068</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0.0059488650635039</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>1464</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>得力</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>149.4425738835937</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>42.27321884483177</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>9.895786995160114</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.8834447206290561</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.0112189345488804</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>1460</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>宏遠</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>138.4743461533372</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>43.670766373656</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>14.965714980227</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.6715920108997665</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.0221472090385823</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>1539</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>巨庭</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>123.9115792744166</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>41.01996164761457</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>12.42177448140319</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.4311370101520761</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-0.0483669154988969</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>瑞利</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>97.8065165318376</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>36.22119172647474</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>9.548114729120066</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.5238506627744138</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>-0.0098910221558056</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>立益</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>96.79947483767459</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>50.35447494261504</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>7.577316565896524</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.444324430479183</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>0.2616461729842577</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
         <v>1535</v>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>中宇</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D83" s="2" t="n">
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
         <v>95.04273226484392</v>
       </c>
-      <c r="E83" s="2" t="n">
+      <c r="E132" s="2" t="n">
         <v>45.95</v>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="2" t="n">
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
         <v>41.51296315772752</v>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>11.64925121688798</v>
-      </c>
-      <c r="J83" s="2" t="n">
+      <c r="I132" s="2" t="n">
+        <v>11.64925120730532</v>
+      </c>
+      <c r="J132" s="2" t="n">
         <v>0.6809031794494452</v>
       </c>
-      <c r="K83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N83" s="2" t="n">
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
         <v>0.1367176228572176</v>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>泰山</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>82.69619041231786</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>49.18930242949487</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>19.30344880184504</v>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>1.495226859884412</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>0.2306917022001046</v>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
